--- a/hpi_scraper/NewsAnnouncements/exa/exa_data.xlsx
+++ b/hpi_scraper/NewsAnnouncements/exa/exa_data.xlsx
@@ -445,7 +445,7 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
@@ -453,7 +453,7 @@
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
@@ -518,37 +518,37 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Singtel gets funding boost from government to strengthen AI push, create high-value roles - The Business Times</t>
+          <t>Singapore's Sea tests AI chatbot Migoo in quiet US foray - The Business Times</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Singtel gets funding boost from government to strengthen AI push, create high-value roles - The Business Times</t>
+          <t>Singapore's Sea tests AI chatbot Migoo in quiet US foray - The Business Times</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>https://www.businesstimes.com.sg/companies-markets/singtel-gets-funding-boost-government-strengthen-ai-push-create-high-value-roles</t>
+          <t>https://www.businesstimes.com.sg/companies-markets/telcos-media-tech/singapores-sea-tests-ai-chatbot-migoo-quiet-us-foray</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -556,11 +556,7 @@
           <t>funding</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Young Zhan Heng</t>
-        </is>
-      </c>
+      <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -575,37 +571,37 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Singtel, KKR-owned STT GDC opens its first South Korean data centre to tap AI boom - The Business Times</t>
+          <t>Singapore-based Sea Ltd seeks to expand to banking, financial services in Vietnam - TNGlobal</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Singtel, KKR-owned STT GDC opens its first South Korean data centre to tap AI boom - The Business Times</t>
+          <t>Singapore-based Sea Ltd seeks to expand to banking, financial services in Vietnam - TNGlobal</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>https://www.businesstimes.com.sg/startups-tech/technology/singtel-kkr-owned-stt-gdc-opens-its-first-south-korean-data-centre-tap-ai-boom</t>
+          <t>https://technode.global/2026/06/01/singapore-based-sea-ltd-seeks-to-expand-to-banking-financial-services-in-vietnam/</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -615,12 +611,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Shikhar Gupta</t>
+          <t>Duc Dao</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -632,37 +628,37 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>KKR, Singtel to fully own data centre powerhouse STT GDC for $6.6 billion amid AI boom | The Straits Times</t>
+          <t>Singapore's Sea sets up AI investment team as part of pivot beyond e-commerce - The Business Times</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>KKR, Singtel to fully own data centre powerhouse STT GDC for $6.6 billion amid AI boom | The Straits Times</t>
+          <t>Singapore's Sea sets up AI investment team as part of pivot beyond e-commerce - The Business Times</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>https://www.straitstimes.com/business/companies-markets/singtel-kkr-consortium-buy-rest-of-st-telemedia-global-data-centres-for-6-6-billion</t>
+          <t>https://www.businesstimes.com.sg/companies-markets/singapores-sea-sets-ai-investment-team-part-pivot-beyond-e-commerce</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -685,52 +681,52 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Singtel Digital InfraCo’s RE:AI and WEKA partner to deliver sovereign AI infrastructure across ASEAN, The AI-Native Telco | TelecomTV</t>
+          <t>Sea establishes AI Center of Excellence in Singapore to drive AI innovation, capability building - TNGlobal</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Singtel Digital InfraCo’s RE:AI and WEKA partner to deliver sovereign AI infrastructure across ASEAN, The AI-Native Telco | TelecomTV</t>
+          <t>Sea establishes AI Center of Excellence in Singapore to drive AI innovation, capability building - TNGlobal</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>https://www.telecomtv.com/content/ai/singtel-digital-infraco-s-re-ai-and-weka-partner-to-deliver-sovereign-ai-infrastructure-across-asean-55635/</t>
+          <t>https://technode.global/2026/04/21/sea-establishes-ai-center-of-excellence-in-singapore-to-drive-ai-innovation-capability-building/</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>funding</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Singtel</t>
+          <t>TechNode Global Staff</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -742,37 +738,37 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Singtel launches US$250M AI growth fund - The Business Times</t>
+          <t>SEA Ltd. Expands to U.S., Launches Migoo AI Chatbot to Boost Growth &amp; Profit :: AktienSensor</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Singtel launches US$250M AI growth fund - The Business Times</t>
+          <t>SEA Ltd. Expands to U.S., Launches Migoo AI Chatbot to Boost Growth &amp; Profit :: AktienSensor</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>https://www.businesstimes.com.sg/companies-markets/singtel-unit-launches-us250-million-global-ai-growth-fund</t>
+          <t>https://aktiensensor.com/articles/sea-ltd.-expands-to-u.s.-launches-migoo-ai-chatbot-to-boost-growth--profit/</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -780,11 +776,7 @@
           <t>funding</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Shikhar Gupta</t>
-        </is>
-      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
